--- a/examples/ecw-export.xlsx
+++ b/examples/ecw-export.xlsx
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -77,6 +77,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -86,12 +98,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D282"/>
+  <dimension ref="A1:D336"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -145,12 +157,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -162,12 +174,12 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -179,12 +191,12 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -196,12 +208,12 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -213,12 +225,12 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -235,7 +247,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -252,12 +264,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
@@ -269,7 +281,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -281,12 +293,12 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -298,12 +310,12 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -315,12 +327,12 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -332,12 +344,12 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -349,12 +361,12 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -371,7 +383,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -388,7 +400,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -405,7 +417,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -422,7 +434,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -439,7 +451,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -451,29 +463,29 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -485,12 +497,12 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -502,12 +514,12 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -519,12 +531,12 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -536,12 +548,12 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -553,12 +565,12 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -570,17 +582,17 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
@@ -592,7 +604,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -604,29 +616,29 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -643,7 +655,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -655,51 +667,46 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">Live Operations Dashboard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BPATEL</t>
-        </is>
-      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Permission to web enable patients</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -711,12 +718,12 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">Security Access Logs</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -728,12 +735,12 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Access Log Report</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -745,12 +752,12 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Administration / Users Configuration</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Change Password</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -762,46 +769,51 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Blast eMsg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BPATEL</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -813,46 +825,46 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -864,29 +876,29 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -898,97 +910,97 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1000,12 +1012,12 @@
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1017,12 +1029,12 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1034,12 +1046,12 @@
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1051,12 +1063,12 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1068,12 +1080,12 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1085,12 +1097,12 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1102,29 +1114,29 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1136,46 +1148,46 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1187,68 +1199,63 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CNGUYEN</t>
-        </is>
-      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1260,46 +1267,46 @@
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Live Operations Dashboard</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1311,12 +1318,12 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Permission to web enable patients</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1328,63 +1335,63 @@
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Security Access Logs</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Access Log Report</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Administration / Users Configuration</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Change Password</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1396,29 +1403,34 @@
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">Blast eMsg</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CNGUYEN</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1430,29 +1442,29 @@
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1464,12 +1476,12 @@
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1481,29 +1493,29 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1515,12 +1527,12 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1532,12 +1544,12 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1549,12 +1561,12 @@
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1566,12 +1578,12 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1583,12 +1595,12 @@
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -1600,63 +1612,63 @@
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -1668,46 +1680,46 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -1719,12 +1731,12 @@
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1734,53 +1746,48 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLEE</t>
-        </is>
-      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -1792,12 +1799,12 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -1809,29 +1816,29 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -1843,29 +1850,29 @@
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -1877,29 +1884,29 @@
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">View Only</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -1911,12 +1918,12 @@
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -1928,12 +1935,12 @@
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">Live Operations Dashboard</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -1945,12 +1952,12 @@
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Permission to web enable patients</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -1962,29 +1969,29 @@
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Security Access Logs</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -1996,12 +2003,12 @@
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Access Log Report</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2013,29 +2020,29 @@
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / Users Configuration</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Change Password</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Blast eMsg</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2045,14 +2052,19 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLEE</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2064,12 +2076,12 @@
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2081,12 +2093,12 @@
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2098,12 +2110,12 @@
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2115,29 +2127,29 @@
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2149,46 +2161,46 @@
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">View Only</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2200,46 +2212,46 @@
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2251,68 +2263,63 @@
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EFOSTER</t>
-        </is>
-      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2324,12 +2331,12 @@
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2341,12 +2348,12 @@
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2358,12 +2365,12 @@
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2375,12 +2382,12 @@
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2392,12 +2399,12 @@
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2409,12 +2416,12 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2426,12 +2433,12 @@
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2443,12 +2450,12 @@
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2460,12 +2467,12 @@
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -2477,46 +2484,46 @@
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -2528,12 +2535,12 @@
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -2545,12 +2552,12 @@
     <row r="145">
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -2562,12 +2569,12 @@
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Live Operations Dashboard</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -2579,12 +2586,12 @@
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Permission to web enable patients</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -2596,12 +2603,12 @@
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -2613,63 +2620,63 @@
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Security Access Logs</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Access Log Report</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Users Configuration</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Change Password</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Blast eMsg</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -2679,48 +2686,53 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EFOSTER</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -2732,46 +2744,46 @@
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -2783,12 +2795,12 @@
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -2798,53 +2810,48 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FMORALES</t>
-        </is>
-      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -2856,12 +2863,12 @@
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -2873,12 +2880,12 @@
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -2890,12 +2897,12 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -2907,29 +2914,29 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -2941,12 +2948,12 @@
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -2958,12 +2965,12 @@
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -2975,29 +2982,29 @@
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3009,12 +3016,12 @@
     <row r="172">
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3026,29 +3033,29 @@
     <row r="173">
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3060,12 +3067,12 @@
     <row r="175">
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3077,34 +3084,34 @@
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3123,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -3128,46 +3135,46 @@
     <row r="179">
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -3179,12 +3186,12 @@
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -3196,12 +3203,12 @@
     <row r="183">
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Live Operations Dashboard</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -3213,46 +3220,46 @@
     <row r="184">
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Permission to web enable patients</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Security Access Logs</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -3264,12 +3271,12 @@
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Access Log Report</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -3281,29 +3288,29 @@
     <row r="188">
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Administration / Users Configuration</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Change Password</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Blast eMsg</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -3313,53 +3320,53 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FMORALES</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GKIM</t>
-        </is>
-      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -3371,12 +3378,12 @@
     <row r="193">
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -3388,17 +3395,17 @@
     <row r="194">
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3417,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3434,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -3444,7 +3451,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -3461,7 +3468,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -3473,12 +3480,12 @@
     <row r="199">
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -3490,12 +3497,12 @@
     <row r="200">
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -3507,12 +3514,12 @@
     <row r="201">
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -3524,12 +3531,12 @@
     <row r="202">
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -3541,17 +3548,17 @@
     <row r="203">
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3570,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3587,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3604,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -3614,7 +3621,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -3626,12 +3633,12 @@
     <row r="208">
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -3643,29 +3650,29 @@
     <row r="209">
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -3677,12 +3684,12 @@
     <row r="211">
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -3694,63 +3701,63 @@
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -3767,12 +3774,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3791,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -3796,12 +3803,12 @@
     <row r="218">
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -3813,12 +3820,12 @@
     <row r="219">
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -3835,97 +3842,92 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Live Operations Dashboard</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">Permission to web enable patients</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HRIVERA</t>
-        </is>
-      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Security Access Logs</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">Access Log Report</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / Users Configuration</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Change Password</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -3937,80 +3939,85 @@
     <row r="226">
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Blast eMsg</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GKIM</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -4022,29 +4029,29 @@
     <row r="231">
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -4056,12 +4063,12 @@
     <row r="233">
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -4073,12 +4080,12 @@
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -4090,12 +4097,12 @@
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -4107,80 +4114,80 @@
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -4192,12 +4199,12 @@
     <row r="241">
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -4209,12 +4216,12 @@
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -4226,12 +4233,12 @@
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -4243,12 +4250,12 @@
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -4260,29 +4267,29 @@
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -4294,29 +4301,29 @@
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -4328,29 +4335,29 @@
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -4362,29 +4369,29 @@
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telehealth</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start video visit</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -4394,36 +4401,31 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ztemp</t>
-        </is>
-      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="B254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -4435,12 +4437,12 @@
     <row r="255">
       <c r="B255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -4452,29 +4454,29 @@
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Live Operations Dashboard</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -4486,12 +4488,12 @@
     <row r="258">
       <c r="B258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Permission to web enable patients</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -4503,12 +4505,12 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -4520,12 +4522,12 @@
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Security Access Logs</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -4537,12 +4539,12 @@
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Logs</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Access Log Report</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -4554,29 +4556,29 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Administration / Users Configuration</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Change Password</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Patient Portal</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Blast eMsg</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -4586,65 +4588,70 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HRIVERA</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -4656,29 +4663,29 @@
     <row r="268">
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -4690,12 +4697,12 @@
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -4707,46 +4714,46 @@
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -4758,12 +4765,12 @@
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -4775,12 +4782,12 @@
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -4792,12 +4799,12 @@
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -4809,63 +4816,63 @@
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -4877,34 +4884,957 @@
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete Payments</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete Refunds</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changing Fee schedule</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPT Codes</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insurances</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete Reviewed Document</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulk Actions</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="inlineStr">
+        <is>
           <t xml:space="preserve">Reports</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Run financial reports</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report - Billing Summary</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reports</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live Operations Dashboard</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Portal</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Permission to web enable patients</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Portal</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logs</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security Access Logs</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logs</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access Log Report</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Users Configuration</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Password</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Portal</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blast eMsg</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ztemp</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Details</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Details</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access Problem List</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Details</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AccountNumber Update</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access to PHI and PII</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress Notes</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lock Chart</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress Notes</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress Notes</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access Patient Orders</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progress Notes</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access/View Superbill</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locked Progress Notes</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit Addendums</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locked Progress Notes</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SureScripts</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SS EPrescription</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SureScripts</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SS Refill Response</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Billing</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batches</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Billing</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close Transactions</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Billing</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow users to lock claims</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Billing</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Billing</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accounts LookUp</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete Payments</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete Refunds</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changing Fee schedule</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPT Codes</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Billing Setup</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insurances</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete Reviewed Document</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulk Actions</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reports</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report - Billing Summary</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reports</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live Operations Dashboard</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Portal</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Permission to web enable patients</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Portal</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logs</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security Access Logs</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logs</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access Log Report</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Users Configuration</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Password</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
